--- a/uploads/SEIBRAS_3.xlsx
+++ b/uploads/SEIBRAS_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james.santos\Documents\28-07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F06B159-67E3-4144-9854-753981902258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555B31BD-F43A-44A0-96D7-BE2044E3526C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="120">
   <si>
     <t>[ KO4829816 3079058651 ]  COMULTADOR ELETRICO IGUINICAO VOLKS</t>
   </si>
@@ -388,9 +388,6 @@
   </si>
   <si>
     <t>CODIGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marca </t>
   </si>
 </sst>
 </file>
@@ -414,7 +411,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -437,14 +434,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -787,10 +796,9 @@
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="3.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>119</v>
       </c>
@@ -809,11 +817,8 @@
       <c r="F1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>15396</v>
       </c>
@@ -821,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
@@ -832,11 +837,8 @@
       <c r="F2" s="1">
         <v>26.19</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>16963</v>
       </c>
@@ -844,7 +846,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>2</v>
@@ -855,11 +857,8 @@
       <c r="F3" s="1">
         <v>16.190000000000001</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>17551</v>
       </c>
@@ -867,7 +866,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -878,11 +877,8 @@
       <c r="F4" s="1">
         <v>6.39</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>17562</v>
       </c>
@@ -890,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>2</v>
@@ -901,11 +897,8 @@
       <c r="F5" s="1">
         <v>27.99</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>17655</v>
       </c>
@@ -913,7 +906,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>2</v>
@@ -924,11 +917,8 @@
       <c r="F6" s="1">
         <v>9.7899999999999991</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>29849</v>
       </c>
@@ -936,7 +926,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>2</v>
@@ -947,11 +937,8 @@
       <c r="F7" s="1">
         <v>21.39</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>101283</v>
       </c>
@@ -959,7 +946,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>2</v>
@@ -970,11 +957,8 @@
       <c r="F8" s="1">
         <v>7.89</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>101349</v>
       </c>
@@ -982,7 +966,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>2</v>
@@ -993,11 +977,8 @@
       <c r="F9" s="1">
         <v>0.35</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>102124</v>
       </c>
@@ -1014,11 +995,8 @@
         <v>10</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>103338</v>
       </c>
@@ -1026,7 +1004,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>2</v>
@@ -1037,11 +1015,8 @@
       <c r="F11" s="1">
         <v>6.19</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>105841</v>
       </c>
@@ -1049,7 +1024,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>2</v>
@@ -1060,11 +1035,8 @@
       <c r="F12" s="1">
         <v>12.69</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>113056</v>
       </c>
@@ -1081,11 +1053,8 @@
         <v>1</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>115412</v>
       </c>
@@ -1093,7 +1062,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>2</v>
@@ -1104,11 +1073,8 @@
       <c r="F14" s="1">
         <v>21.39</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>115456</v>
       </c>
@@ -1125,11 +1091,8 @@
         <v>10</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>116471</v>
       </c>
@@ -1146,11 +1109,8 @@
         <v>10</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>116602</v>
       </c>
@@ -1158,7 +1118,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>2</v>
@@ -1169,11 +1129,8 @@
       <c r="F17" s="1">
         <v>151.99</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>116848</v>
       </c>
@@ -1181,7 +1138,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>2</v>
@@ -1192,11 +1149,8 @@
       <c r="F18" s="1">
         <v>22.79</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116985</v>
       </c>
@@ -1204,7 +1158,7 @@
         <v>19</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>2</v>
@@ -1215,11 +1169,8 @@
       <c r="F19" s="1">
         <v>248.99</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>119049</v>
       </c>
@@ -1236,11 +1187,8 @@
         <v>2</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>120539</v>
       </c>
@@ -1248,7 +1196,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>2</v>
@@ -1259,11 +1207,8 @@
       <c r="F21" s="1">
         <v>114.99</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>120713</v>
       </c>
@@ -1280,11 +1225,8 @@
         <v>1</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>132858</v>
       </c>
@@ -1303,11 +1245,8 @@
       <c r="F23" s="1">
         <v>292.99</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>132907</v>
       </c>
@@ -1324,11 +1263,8 @@
         <v>1</v>
       </c>
       <c r="F24" s="1"/>
-      <c r="G24" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>133161</v>
       </c>
@@ -1336,7 +1272,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>2</v>
@@ -1347,11 +1283,8 @@
       <c r="F25" s="1">
         <v>10.29</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>134835</v>
       </c>
@@ -1359,7 +1292,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>2</v>
@@ -1370,11 +1303,8 @@
       <c r="F26" s="1">
         <v>47.49</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>136147</v>
       </c>
@@ -1382,7 +1312,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>2</v>
@@ -1393,11 +1323,8 @@
       <c r="F27" s="1">
         <v>58.99</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>137391</v>
       </c>
@@ -1405,7 +1332,7 @@
         <v>29</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>2</v>
@@ -1416,11 +1343,8 @@
       <c r="F28" s="1">
         <v>86.99</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>137480</v>
       </c>
@@ -1428,7 +1352,7 @@
         <v>30</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>2</v>
@@ -1439,11 +1363,8 @@
       <c r="F29" s="1">
         <v>32.19</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>141891</v>
       </c>
@@ -1460,11 +1381,8 @@
         <v>2</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>142660</v>
       </c>
@@ -1472,7 +1390,7 @@
         <v>32</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>2</v>
@@ -1483,11 +1401,8 @@
       <c r="F31" s="1">
         <v>4.1900000000000004</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>145597</v>
       </c>
@@ -1495,7 +1410,7 @@
         <v>33</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>2</v>
@@ -1506,11 +1421,8 @@
       <c r="F32" s="1">
         <v>50.19</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>146832</v>
       </c>
@@ -1527,11 +1439,8 @@
         <v>1</v>
       </c>
       <c r="F33" s="1"/>
-      <c r="G33" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>164004</v>
       </c>
@@ -1539,7 +1448,7 @@
         <v>35</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>2</v>
@@ -1550,11 +1459,8 @@
       <c r="F34" s="1">
         <v>81.89</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>167357</v>
       </c>
@@ -1562,7 +1468,7 @@
         <v>36</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>2</v>
@@ -1573,11 +1479,8 @@
       <c r="F35" s="1">
         <v>16.690000000000001</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>173869</v>
       </c>
@@ -1585,7 +1488,7 @@
         <v>37</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>2</v>
@@ -1596,11 +1499,8 @@
       <c r="F36" s="1">
         <v>31.99</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>180520</v>
       </c>
@@ -1608,7 +1508,7 @@
         <v>38</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>2</v>
@@ -1619,11 +1519,8 @@
       <c r="F37" s="1">
         <v>51.99</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>184187</v>
       </c>
@@ -1631,7 +1528,7 @@
         <v>39</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>2</v>
@@ -1642,11 +1539,8 @@
       <c r="F38" s="1">
         <v>6.79</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>184617</v>
       </c>
@@ -1663,11 +1557,8 @@
         <v>3</v>
       </c>
       <c r="F39" s="1"/>
-      <c r="G39" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>192126</v>
       </c>
@@ -1684,11 +1575,8 @@
         <v>1</v>
       </c>
       <c r="F40" s="1"/>
-      <c r="G40" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>192401</v>
       </c>
@@ -1696,7 +1584,7 @@
         <v>42</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>2</v>
@@ -1707,11 +1595,8 @@
       <c r="F41" s="1">
         <v>13.39</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>198048</v>
       </c>
@@ -1730,11 +1615,8 @@
       <c r="F42" s="1">
         <v>12.79</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>203543</v>
       </c>
@@ -1742,7 +1624,7 @@
         <v>45</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>2</v>
@@ -1753,11 +1635,8 @@
       <c r="F43" s="1">
         <v>19.89</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>206386</v>
       </c>
@@ -1774,11 +1653,8 @@
         <v>4</v>
       </c>
       <c r="F44" s="1"/>
-      <c r="G44" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>209705</v>
       </c>
@@ -1795,11 +1671,8 @@
         <v>1</v>
       </c>
       <c r="F45" s="1"/>
-      <c r="G45" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>212579</v>
       </c>
@@ -1807,7 +1680,7 @@
         <v>48</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>2</v>
@@ -1818,11 +1691,8 @@
       <c r="F46" s="1">
         <v>399.99</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>214696</v>
       </c>
@@ -1830,7 +1700,7 @@
         <v>50</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>2</v>
@@ -1841,11 +1711,8 @@
       <c r="F47" s="1">
         <v>9.89</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>215088</v>
       </c>
@@ -1862,11 +1729,8 @@
         <v>2</v>
       </c>
       <c r="F48" s="1"/>
-      <c r="G48" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>215187</v>
       </c>
@@ -1874,7 +1738,7 @@
         <v>52</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>2</v>
@@ -1885,11 +1749,8 @@
       <c r="F49" s="1">
         <v>70.59</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>215250</v>
       </c>
@@ -1906,11 +1767,8 @@
         <v>1</v>
       </c>
       <c r="F50" s="1"/>
-      <c r="G50" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>215321</v>
       </c>
@@ -1918,7 +1776,7 @@
         <v>54</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>2</v>
@@ -1929,11 +1787,8 @@
       <c r="F51" s="1">
         <v>23.49</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>215348</v>
       </c>
@@ -1950,11 +1805,8 @@
         <v>10</v>
       </c>
       <c r="F52" s="1"/>
-      <c r="G52" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>215350</v>
       </c>
@@ -1971,11 +1823,8 @@
         <v>10</v>
       </c>
       <c r="F53" s="1"/>
-      <c r="G53" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>215382</v>
       </c>
@@ -1992,11 +1841,8 @@
         <v>10</v>
       </c>
       <c r="F54" s="1"/>
-      <c r="G54" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>215395</v>
       </c>
@@ -2013,11 +1859,8 @@
         <v>10</v>
       </c>
       <c r="F55" s="1"/>
-      <c r="G55" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>215457</v>
       </c>
@@ -2034,11 +1877,8 @@
         <v>4</v>
       </c>
       <c r="F56" s="1"/>
-      <c r="G56" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>215465</v>
       </c>
@@ -2046,7 +1886,7 @@
         <v>60</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>61</v>
@@ -2057,11 +1897,8 @@
       <c r="F57" s="1">
         <v>8.39</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>215473</v>
       </c>
@@ -2069,7 +1906,7 @@
         <v>62</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>2</v>
@@ -2080,11 +1917,8 @@
       <c r="F58" s="1">
         <v>15.19</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>215478</v>
       </c>
@@ -2092,7 +1926,7 @@
         <v>63</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>61</v>
@@ -2103,11 +1937,8 @@
       <c r="F59" s="1">
         <v>18.989999999999998</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>215487</v>
       </c>
@@ -2115,7 +1946,7 @@
         <v>64</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>61</v>
@@ -2126,11 +1957,8 @@
       <c r="F60" s="1">
         <v>27.29</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>215489</v>
       </c>
@@ -2138,7 +1966,7 @@
         <v>65</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>2</v>
@@ -2149,11 +1977,8 @@
       <c r="F61" s="1">
         <v>162.99</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>215490</v>
       </c>
@@ -2170,11 +1995,8 @@
         <v>5</v>
       </c>
       <c r="F62" s="1"/>
-      <c r="G62" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>215515</v>
       </c>
@@ -2191,11 +2013,8 @@
         <v>5</v>
       </c>
       <c r="F63" s="1"/>
-      <c r="G63" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>215519</v>
       </c>
@@ -2203,7 +2022,7 @@
         <v>68</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>2</v>
@@ -2213,9 +2032,6 @@
       </c>
       <c r="F64" s="1">
         <v>7.89</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -2226,7 +2042,7 @@
         <v>69</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>2</v>
@@ -2236,9 +2052,6 @@
       </c>
       <c r="F65" s="1">
         <v>5.89</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -2249,7 +2062,7 @@
         <v>70</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>61</v>
@@ -2259,9 +2072,6 @@
       </c>
       <c r="F66" s="1">
         <v>9.99</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -2272,7 +2082,7 @@
         <v>71</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>2</v>
@@ -2282,9 +2092,6 @@
       </c>
       <c r="F67" s="1">
         <v>13.19</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -2295,7 +2102,7 @@
         <v>72</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>2</v>
@@ -2305,9 +2112,6 @@
       </c>
       <c r="F68" s="1">
         <v>13.19</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -2318,7 +2122,7 @@
         <v>73</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>2</v>
@@ -2328,9 +2132,6 @@
       </c>
       <c r="F69" s="1">
         <v>6.29</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -2341,7 +2142,7 @@
         <v>74</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>2</v>
@@ -2351,9 +2152,6 @@
       </c>
       <c r="F70" s="1">
         <v>45.39</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
@@ -2364,7 +2162,7 @@
         <v>75</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>2</v>
@@ -2374,9 +2172,6 @@
       </c>
       <c r="F71" s="1">
         <v>4.59</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -2398,9 +2193,6 @@
       <c r="F72" s="1">
         <v>47.39</v>
       </c>
-      <c r="G72" s="2" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
@@ -2410,7 +2202,7 @@
         <v>77</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>2</v>
@@ -2421,9 +2213,7 @@
       <c r="F73" s="1">
         <v>3.45</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="G73" s="3"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
@@ -2433,7 +2223,7 @@
         <v>78</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>2</v>
@@ -2444,9 +2234,7 @@
       <c r="F74" s="1">
         <v>65.989999999999995</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="G74" s="3"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
@@ -2456,7 +2244,7 @@
         <v>79</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>2</v>
@@ -2466,9 +2254,6 @@
       </c>
       <c r="F75" s="1">
         <v>0.25</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -2479,7 +2264,7 @@
         <v>80</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>2</v>
@@ -2489,9 +2274,6 @@
       </c>
       <c r="F76" s="1">
         <v>6.79</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -2511,9 +2293,6 @@
         <v>2</v>
       </c>
       <c r="F77" s="1"/>
-      <c r="G77" s="2" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
@@ -2532,9 +2311,6 @@
         <v>2</v>
       </c>
       <c r="F78" s="1"/>
-      <c r="G78" s="2" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
@@ -2553,9 +2329,6 @@
         <v>2</v>
       </c>
       <c r="F79" s="1"/>
-      <c r="G79" s="2" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
@@ -2565,7 +2338,7 @@
         <v>84</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>2</v>
@@ -2576,11 +2349,8 @@
       <c r="F80" s="1">
         <v>83.39</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>218123</v>
       </c>
@@ -2588,7 +2358,7 @@
         <v>85</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>2</v>
@@ -2599,11 +2369,8 @@
       <c r="F81" s="1">
         <v>4.99</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>218692</v>
       </c>
@@ -2620,11 +2387,8 @@
         <v>1</v>
       </c>
       <c r="F82" s="1"/>
-      <c r="G82" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>218739</v>
       </c>
@@ -2632,7 +2396,7 @@
         <v>88</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>2</v>
@@ -2642,9 +2406,6 @@
       </c>
       <c r="F83" s="1">
         <v>30.09</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
